--- a/inputs/templates/TEMPLATE FONDO LIQUIDEZ Permanente.xlsx
+++ b/inputs/templates/TEMPLATE FONDO LIQUIDEZ Permanente.xlsx
@@ -25,7 +25,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
@@ -34,6 +34,7 @@
     <numFmt numFmtId="169" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="170" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="171" formatCode="0.000%"/>
+    <numFmt numFmtId="172" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -357,7 +358,7 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -588,6 +589,7 @@
     <xf numFmtId="164" fontId="26" fillId="15" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="26" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="6"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2024,7 +2026,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -2076,7 +2078,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -2171,7 +2173,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CL"/>
         </a:p>
@@ -2960,7 +2962,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t/>
+                <a:t>None</a:t>
               </a:r>
               <a:endParaRPr lang="es-CL"/>
             </a:p>
@@ -2992,7 +2994,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -3029,7 +3031,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CL"/>
         </a:p>
@@ -4349,7 +4351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK249"/>
+  <dimension ref="A1:BK251"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.28515625" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" style="9" min="1" max="2"/>
@@ -6647,7 +6649,7 @@
         </is>
       </c>
       <c r="AW19" s="79" t="n">
-        <v>46142</v>
+        <v>46203</v>
       </c>
       <c r="AX19" s="37">
         <f>EOMONTH($AW19,AX18)+6</f>
@@ -7055,8 +7057,14 @@
         <f>+S23/R23-1</f>
         <v/>
       </c>
-      <c r="AI22" s="15" t="n"/>
-      <c r="AJ22" s="15" t="n"/>
+      <c r="AI22" s="15">
+        <f>+T23/S23-1</f>
+        <v/>
+      </c>
+      <c r="AJ22" s="15">
+        <f>+U23/T23-1</f>
+        <v/>
+      </c>
       <c r="AK22" s="15" t="n"/>
       <c r="AL22" s="15" t="n"/>
       <c r="AM22" s="15" t="n"/>
@@ -7064,7 +7072,7 @@
       <c r="AO22" s="15" t="n"/>
       <c r="AP22" s="15" t="n"/>
       <c r="AQ22" s="29">
-        <f>+(S23/P23-1)/COUNTA(AE22:AP22)*12</f>
+        <f>+(U23/P23-1)/COUNTA(AE22:AJ22)*12</f>
         <v/>
       </c>
       <c r="AV22" s="34" t="inlineStr">
@@ -7123,7 +7131,14 @@
         <f>+B249</f>
         <v/>
       </c>
-      <c r="U23" s="25" t="n"/>
+      <c r="T23">
+        <f>+B250</f>
+        <v/>
+      </c>
+      <c r="U23" s="25">
+        <f>+B251</f>
+        <v/>
+      </c>
       <c r="Y23" s="25" t="n"/>
       <c r="AD23" s="32" t="n"/>
       <c r="AE23" s="15" t="n"/>
@@ -8401,8 +8416,14 @@
         <f>+G249</f>
         <v/>
       </c>
-      <c r="T37" s="108" t="n"/>
-      <c r="U37" s="108" t="n"/>
+      <c r="T37" s="108">
+        <f>+G250</f>
+        <v/>
+      </c>
+      <c r="U37" s="108">
+        <f>+G251</f>
+        <v/>
+      </c>
       <c r="V37" s="108" t="n"/>
       <c r="W37" s="108" t="n"/>
       <c r="X37" s="108" t="n"/>
@@ -8536,8 +8557,16 @@
         <f>+(S37/R37-1)</f>
         <v/>
       </c>
+      <c r="AI38">
+        <f>+T37/S37-1</f>
+        <v/>
+      </c>
+      <c r="AJ38">
+        <f>+U37/T37-1</f>
+        <v/>
+      </c>
       <c r="AQ38" s="29">
-        <f>+(S37/P37-1)/COUNTA(AE38:AP38)*12</f>
+        <f>+(U37/P37-1)/COUNTA(AE38:AJ38)*12</f>
         <v/>
       </c>
       <c r="AR38" s="32" t="inlineStr">
@@ -10094,6 +10123,14 @@
         <f>+K249</f>
         <v/>
       </c>
+      <c r="T51">
+        <f>+K250</f>
+        <v/>
+      </c>
+      <c r="U51">
+        <f>+K251</f>
+        <v/>
+      </c>
       <c r="AD51" s="27" t="n">
         <v>2026</v>
       </c>
@@ -10113,8 +10150,14 @@
         <f>+(S51/R51-1)</f>
         <v/>
       </c>
-      <c r="AI51" s="15" t="n"/>
-      <c r="AJ51" s="15" t="n"/>
+      <c r="AI51" s="15">
+        <f>+T51/S51-1</f>
+        <v/>
+      </c>
+      <c r="AJ51" s="15">
+        <f>+U51/T51-1</f>
+        <v/>
+      </c>
       <c r="AK51" s="15" t="n"/>
       <c r="AL51" s="15" t="n"/>
       <c r="AM51" s="15" t="n"/>
@@ -10122,7 +10165,7 @@
       <c r="AO51" s="15" t="n"/>
       <c r="AP51" s="15" t="n"/>
       <c r="AQ51" s="29">
-        <f>+(S51/P51-1)/COUNTA(AE51:AP51)*12</f>
+        <f>+(U51/P51-1)/COUNTA(AE51:AJ51)*12</f>
         <v/>
       </c>
       <c r="AR51" s="15" t="n"/>
@@ -17582,6 +17625,96 @@
       </c>
       <c r="M249" s="25">
         <f>+M248*(1+L249)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="122" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B250" t="n">
+        <v>26535.18</v>
+      </c>
+      <c r="C250">
+        <f>(B250/B249-1)/(A250-A249)*30</f>
+        <v/>
+      </c>
+      <c r="D250">
+        <f>+D249*(1+C250)</f>
+        <v/>
+      </c>
+      <c r="F250" s="122" t="n">
+        <v>46173</v>
+      </c>
+      <c r="G250" t="n">
+        <v>1209.7461</v>
+      </c>
+      <c r="H250">
+        <f>+G250+$S$148+$S$150+$S$152+$S$154+$S$156+$S$158</f>
+        <v/>
+      </c>
+      <c r="I250">
+        <f>+(H250/H249-1)/(F250-F249)*30</f>
+        <v/>
+      </c>
+      <c r="J250">
+        <f>+J249*(1+I250)</f>
+        <v/>
+      </c>
+      <c r="K250" t="n">
+        <v>6368.94</v>
+      </c>
+      <c r="L250">
+        <f>+(K250/K249-1)/(F250-F249)*30</f>
+        <v/>
+      </c>
+      <c r="M250">
+        <f>+M249*(1+L250)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="122" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B251" t="n">
+        <v>26634.69</v>
+      </c>
+      <c r="C251">
+        <f>(B251/B250-1)/(A251-A250)*30</f>
+        <v/>
+      </c>
+      <c r="D251">
+        <f>+D250*(1+C251)</f>
+        <v/>
+      </c>
+      <c r="F251" s="122" t="n">
+        <v>46203</v>
+      </c>
+      <c r="G251" t="n">
+        <v>1216.1979</v>
+      </c>
+      <c r="H251">
+        <f>+G251+$S$148+$S$150+$S$152+$S$154+$S$156+$S$158</f>
+        <v/>
+      </c>
+      <c r="I251">
+        <f>+(H251/H250-1)/(F251-F250)*30</f>
+        <v/>
+      </c>
+      <c r="J251">
+        <f>+J250*(1+I251)</f>
+        <v/>
+      </c>
+      <c r="K251" t="n">
+        <v>6385.6713</v>
+      </c>
+      <c r="L251">
+        <f>+(K251/K250-1)/(F251-F250)*30</f>
+        <v/>
+      </c>
+      <c r="M251">
+        <f>+M250*(1+L251)</f>
         <v/>
       </c>
     </row>
